--- a/tame_output/ON/bt/strategyON_20240120.xlsx
+++ b/tame_output/ON/bt/strategyON_20240120.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.7%</t>
+          <t>451.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.8%</t>
+          <t>100.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1247,11 +1247,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>129.9%</t>
+          <t>129.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1847"/>
+  <dimension ref="A1:G1848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.260795497384933</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44042,6 +44042,29 @@
       </c>
       <c r="G1847" t="n">
         <v>4.469315288241491</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="2" t="n">
+        <v>45310</v>
+      </c>
+      <c r="B1848" t="n">
+        <v>3.27155618464155</v>
+      </c>
+      <c r="C1848" t="n">
+        <v>3.116946666549951</v>
+      </c>
+      <c r="D1848" t="n">
+        <v>1.642564256989806</v>
+      </c>
+      <c r="E1848" t="n">
+        <v>3.773615945032127</v>
+      </c>
+      <c r="F1848" t="n">
+        <v>2.254784130445677</v>
+      </c>
+      <c r="G1848" t="n">
+        <v>4.469817144817357</v>
       </c>
     </row>
   </sheetData>
